--- a/data/Skills.xlsx
+++ b/data/Skills.xlsx
@@ -440,19 +440,19 @@
         <v>护盾值</v>
       </c>
       <c r="N1" t="str">
+        <v>免疫效果</v>
+      </c>
+      <c r="O1" t="str">
         <v>速度提升</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>持续时间(ms)</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>金币加成</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
         <v>增加秒数</v>
-      </c>
-      <c r="R1" t="str">
-        <v>防御力加成</v>
       </c>
       <c r="S1" t="str">
         <v>攻击力加成</v>
@@ -461,16 +461,16 @@
         <v>暴击率加成</v>
       </c>
       <c r="U1" t="str">
-        <v>免疫效果</v>
+        <v>暴伤加成</v>
       </c>
       <c r="V1" t="str">
+        <v>防御力加成</v>
+      </c>
+      <c r="W1" t="str">
         <v>复活效果</v>
       </c>
-      <c r="W1" t="str">
+      <c r="X1" t="str">
         <v>百分比治疗</v>
-      </c>
-      <c r="X1" t="str">
-        <v>暴伤加成</v>
       </c>
       <c r="Y1" t="str">
         <v>经验加成</v>
@@ -479,13 +479,13 @@
         <v>生命加成</v>
       </c>
       <c r="AA1" t="str">
-        <v>星星分数加成</v>
+        <v>连击加成</v>
       </c>
       <c r="AB1" t="str">
-        <v>连击加成</v>
+        <v>掉落率加成</v>
       </c>
       <c r="AC1" t="str">
-        <v>掉落率加成</v>
+        <v>灵辉加成</v>
       </c>
       <c r="AD1" t="str">
         <v>闪避加成</v>
@@ -499,7 +499,7 @@
         <v>skill_fireball</v>
       </c>
       <c r="C2" t="str">
-        <v>火球术</v>
+        <v>火灵光·迸发</v>
       </c>
       <c r="D2" t="str">
         <v>attack</v>
@@ -511,7 +511,7 @@
         <v>30</v>
       </c>
       <c r="G2" t="str">
-        <v>发射一个火球造成伤害</v>
+        <v>火行灵光在触碰点引爆，灼烧邪灵的紊乱能量层</v>
       </c>
       <c r="H2" t="str">
         <v>🔥</v>
@@ -531,7 +531,7 @@
         <v>skill_ice_arrow</v>
       </c>
       <c r="C3" t="str">
-        <v>冰箭</v>
+        <v>水灵光·穿透</v>
       </c>
       <c r="D3" t="str">
         <v>attack</v>
@@ -543,7 +543,7 @@
         <v>25</v>
       </c>
       <c r="G3" t="str">
-        <v>射出冰箭穿透敌人</v>
+        <v>凝聚水行灵光为一线，穿透邪灵的能量外壳</v>
       </c>
       <c r="H3" t="str">
         <v>🏹</v>
@@ -563,7 +563,7 @@
         <v>skill_lightning</v>
       </c>
       <c r="C4" t="str">
-        <v>闪电链</v>
+        <v>金灵光·链击</v>
       </c>
       <c r="D4" t="str">
         <v>attack</v>
@@ -575,7 +575,7 @@
         <v>35</v>
       </c>
       <c r="G4" t="str">
-        <v>召唤闪电攻击敌人</v>
+        <v>金行灵光在邪灵之间跳跃传导，紊乱能量加速了传导</v>
       </c>
       <c r="H4" t="str">
         <v>⚡</v>
@@ -595,7 +595,7 @@
         <v>skill_wind_slash</v>
       </c>
       <c r="C5" t="str">
-        <v>风刃</v>
+        <v>木灵光·刃舞</v>
       </c>
       <c r="D5" t="str">
         <v>attack</v>
@@ -607,7 +607,7 @@
         <v>28</v>
       </c>
       <c r="G5" t="str">
-        <v>释放锋利的风刃</v>
+        <v>木行灵光在邪灵群中弹射切割</v>
       </c>
       <c r="H5" t="str">
         <v>💨</v>
@@ -627,7 +627,7 @@
         <v>skill_ice_shard</v>
       </c>
       <c r="C6" t="str">
-        <v>冰晶冲击</v>
+        <v>水灵光·冲击</v>
       </c>
       <c r="D6" t="str">
         <v>attack</v>
@@ -639,10 +639,10 @@
         <v>45</v>
       </c>
       <c r="G6" t="str">
-        <v>召唤冰晶攻击敌人</v>
+        <v>凝聚水行灵光直接冲击邪灵的紊乱核心</v>
       </c>
       <c r="H6" t="str">
-        <v>❄️</v>
+        <v>💧</v>
       </c>
       <c r="I6" t="str">
         <v>damage</v>
@@ -659,7 +659,7 @@
         <v>skill_meteor</v>
       </c>
       <c r="C7" t="str">
-        <v>陨石坠落</v>
+        <v>土灵光·沉坠</v>
       </c>
       <c r="D7" t="str">
         <v>attack</v>
@@ -671,7 +671,7 @@
         <v>50</v>
       </c>
       <c r="G7" t="str">
-        <v>召唤陨石从天而降</v>
+        <v>土行灵光从天而降，以厚重压碎邪灵的屏障</v>
       </c>
       <c r="H7" t="str">
         <v>☄️</v>
@@ -691,7 +691,7 @@
         <v>skill_thunder_storm</v>
       </c>
       <c r="C8" t="str">
-        <v>雷暴</v>
+        <v>金灵光·雷暴</v>
       </c>
       <c r="D8" t="str">
         <v>attack</v>
@@ -703,7 +703,7 @@
         <v>48</v>
       </c>
       <c r="G8" t="str">
-        <v>召唤雷暴覆盖战场</v>
+        <v>金行灵光在战场上形成密集的高频能场</v>
       </c>
       <c r="H8" t="str">
         <v>🌩️</v>
@@ -723,7 +723,7 @@
         <v>skill_blizzard</v>
       </c>
       <c r="C9" t="str">
-        <v>暴风雪</v>
+        <v>水灵光·暴雪</v>
       </c>
       <c r="D9" t="str">
         <v>attack</v>
@@ -735,7 +735,7 @@
         <v>42</v>
       </c>
       <c r="G9" t="str">
-        <v>释放冰风暴冻结一切</v>
+        <v>水行灵光冻结一大片邪灵的活动</v>
       </c>
       <c r="H9" t="str">
         <v>🌨️</v>
@@ -755,7 +755,7 @@
         <v>skill_inferno</v>
       </c>
       <c r="C10" t="str">
-        <v>地狱火</v>
+        <v>火灵光·燎原</v>
       </c>
       <c r="D10" t="str">
         <v>attack</v>
@@ -767,7 +767,7 @@
         <v>55</v>
       </c>
       <c r="G10" t="str">
-        <v>召唤地狱之火焚烧敌人</v>
+        <v>火行灵光在战场蔓延，持续灼烧邪灵</v>
       </c>
       <c r="H10" t="str">
         <v>🔥</v>
@@ -787,7 +787,7 @@
         <v>skill_star_burst</v>
       </c>
       <c r="C11" t="str">
-        <v>星爆</v>
+        <v>灵光爆发</v>
       </c>
       <c r="D11" t="str">
         <v>attack</v>
@@ -799,7 +799,7 @@
         <v>60</v>
       </c>
       <c r="G11" t="str">
-        <v>引爆星辰之力</v>
+        <v>积蓄的灵能在瞬间释放，一次性冲击全场邪灵</v>
       </c>
       <c r="H11" t="str">
         <v>💥</v>
@@ -819,7 +819,7 @@
         <v>skill_dragon_breath</v>
       </c>
       <c r="C12" t="str">
-        <v>龙息</v>
+        <v>鼎纹龙息</v>
       </c>
       <c r="D12" t="str">
         <v>attack</v>
@@ -831,7 +831,7 @@
         <v>58</v>
       </c>
       <c r="G12" t="str">
-        <v>释放龙之吐息</v>
+        <v>龙纹鼎灵的古灵之力——将沉睡的龙威转化为一次灵光吐息</v>
       </c>
       <c r="H12" t="str">
         <v>🐉</v>
@@ -851,7 +851,7 @@
         <v>skill_void_strike</v>
       </c>
       <c r="C13" t="str">
-        <v>虚空斩</v>
+        <v>灵脉共振</v>
       </c>
       <c r="D13" t="str">
         <v>attack</v>
@@ -863,7 +863,7 @@
         <v>55</v>
       </c>
       <c r="G13" t="str">
-        <v>撕裂虚空的致命一击</v>
+        <v>利用灵脉的能量共振传递攻击，穿过邪灵的物质屏障</v>
       </c>
       <c r="H13" t="str">
         <v>🌑</v>
@@ -883,7 +883,7 @@
         <v>skill_holy_light</v>
       </c>
       <c r="C14" t="str">
-        <v>圣光裁决</v>
+        <v>乾元灵光·裁决</v>
       </c>
       <c r="D14" t="str">
         <v>attack</v>
@@ -895,10 +895,10 @@
         <v>62</v>
       </c>
       <c r="G14" t="str">
-        <v>神圣之光审判邪恶</v>
+        <v>高纯度灵光直射邪灵的紊乱核心——秩序排斥混乱</v>
       </c>
       <c r="H14" t="str">
-        <v>✝️</v>
+        <v>✨</v>
       </c>
       <c r="I14" t="str">
         <v>damage</v>
@@ -915,7 +915,7 @@
         <v>skill_star_devour</v>
       </c>
       <c r="C15" t="str">
-        <v>星辰吞噬</v>
+        <v>灵光同调</v>
       </c>
       <c r="D15" t="str">
         <v>attack</v>
@@ -927,7 +927,7 @@
         <v>50</v>
       </c>
       <c r="G15" t="str">
-        <v>释放虚空之力攻击，吸取伤害的30%回复生命</v>
+        <v>与邪灵的紊乱能量建立短暂共振，抽取其中残余的有序灵能修复自身</v>
       </c>
       <c r="H15" t="str">
         <v>🌑</v>
@@ -950,7 +950,7 @@
         <v>skill_galaxy_burst</v>
       </c>
       <c r="C16" t="str">
-        <v>星河毁灭</v>
+        <v>灵光洪流</v>
       </c>
       <c r="D16" t="str">
         <v>attack</v>
@@ -962,10 +962,10 @@
         <v>90</v>
       </c>
       <c r="G16" t="str">
-        <v>引爆整个星河的力量</v>
+        <v>积满释放的全部灵能化为一次覆盖全场的冲击</v>
       </c>
       <c r="H16" t="str">
-        <v>🌌</v>
+        <v>🔮</v>
       </c>
       <c r="I16" t="str">
         <v>damage</v>
@@ -982,7 +982,7 @@
         <v>skill_cosmic_annihilation</v>
       </c>
       <c r="C17" t="str">
-        <v>宇宙湮灭</v>
+        <v>归一灵光</v>
       </c>
       <c r="D17" t="str">
         <v>attack</v>
@@ -994,10 +994,10 @@
         <v>100</v>
       </c>
       <c r="G17" t="str">
-        <v>宇宙终极毁灭之力</v>
+        <v>五灵光汇聚于一点，彻底瓦解大型邪灵的能量结构</v>
       </c>
       <c r="H17" t="str">
-        <v>💀</v>
+        <v>🔻</v>
       </c>
       <c r="I17" t="str">
         <v>damage</v>
@@ -1014,7 +1014,7 @@
         <v>skill_heal</v>
       </c>
       <c r="C18" t="str">
-        <v>治愈</v>
+        <v>愈灵光</v>
       </c>
       <c r="D18" t="str">
         <v>support</v>
@@ -1026,7 +1026,7 @@
         <v>40</v>
       </c>
       <c r="G18" t="str">
-        <v>恢复生命值</v>
+        <v>灵光抚过身体，修复紊乱能量造成的侵蚀</v>
       </c>
       <c r="H18" t="str">
         <v>💚</v>
@@ -1046,7 +1046,7 @@
         <v>skill_shield</v>
       </c>
       <c r="C19" t="str">
-        <v>护盾</v>
+        <v>守灵光</v>
       </c>
       <c r="D19" t="str">
         <v>support</v>
@@ -1058,7 +1058,7 @@
         <v>35</v>
       </c>
       <c r="G19" t="str">
-        <v>获得护盾抵挡伤害</v>
+        <v>凝聚一层灵光幕，短暂阻隔邪灵的攻击</v>
       </c>
       <c r="H19" t="str">
         <v>🛡️</v>
@@ -1078,7 +1078,7 @@
         <v>skill_speed_up</v>
       </c>
       <c r="C20" t="str">
-        <v>加速</v>
+        <v>迅灵光</v>
       </c>
       <c r="D20" t="str">
         <v>support</v>
@@ -1090,7 +1090,7 @@
         <v>45</v>
       </c>
       <c r="G20" t="str">
-        <v>提升攻击速度</v>
+        <v>灵光加持，操作节奏被短暂提升</v>
       </c>
       <c r="H20" t="str">
         <v>👟</v>
@@ -1098,10 +1098,10 @@
       <c r="I20" t="str">
         <v>speed</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>1.2</v>
       </c>
-      <c r="O20">
+      <c r="P20">
         <v>15</v>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
         <v>skill_lucky_star</v>
       </c>
       <c r="C21" t="str">
-        <v>幸运星</v>
+        <v>金运灵光·赐福</v>
       </c>
       <c r="D21" t="str">
         <v>support</v>
@@ -1125,7 +1125,7 @@
         <v>50</v>
       </c>
       <c r="G21" t="str">
-        <v>双倍金币掉落</v>
+        <v>金运灵光在战场上停留期间，掉落的灵币增加</v>
       </c>
       <c r="H21" t="str">
         <v>🍀</v>
@@ -1133,10 +1133,10 @@
       <c r="I21" t="str">
         <v>gold</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>20</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>2</v>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>skill_time_extend</v>
       </c>
       <c r="C22" t="str">
-        <v>时间延长</v>
+        <v>时序灵光·延续</v>
       </c>
       <c r="D22" t="str">
         <v>support</v>
@@ -1160,7 +1160,7 @@
         <v>60</v>
       </c>
       <c r="G22" t="str">
-        <v>增加游戏时间</v>
+        <v>时序灵光拉伸了此地的灵场，战斗得以延长</v>
       </c>
       <c r="H22" t="str">
         <v>⏰</v>
@@ -1168,7 +1168,7 @@
       <c r="I22" t="str">
         <v>time</v>
       </c>
-      <c r="Q22">
+      <c r="R22">
         <v>10</v>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
         <v>skill_greater_heal</v>
       </c>
       <c r="C23" t="str">
-        <v>强力治愈</v>
+        <v>大愈灵光</v>
       </c>
       <c r="D23" t="str">
         <v>support</v>
@@ -1192,7 +1192,7 @@
         <v>55</v>
       </c>
       <c r="G23" t="str">
-        <v>大幅恢复生命值</v>
+        <v>积蓄更多灵能进行一次深层修复</v>
       </c>
       <c r="H23" t="str">
         <v>💖</v>
@@ -1212,7 +1212,7 @@
         <v>skill_iron_skin</v>
       </c>
       <c r="C24" t="str">
-        <v>铁壁</v>
+        <v>青铜灵光·坚壁</v>
       </c>
       <c r="D24" t="str">
         <v>support</v>
@@ -1224,7 +1224,7 @@
         <v>50</v>
       </c>
       <c r="G24" t="str">
-        <v>获得护盾和防御提升</v>
+        <v>鼎魂的古灵共鸣——将灵光化作坚不可摧的防御层</v>
       </c>
       <c r="H24" t="str">
         <v>🏰</v>
@@ -1235,7 +1235,7 @@
       <c r="M24">
         <v>60</v>
       </c>
-      <c r="R24">
+      <c r="V24">
         <v>20</v>
       </c>
     </row>
@@ -1247,7 +1247,7 @@
         <v>skill_star_blessing</v>
       </c>
       <c r="C25" t="str">
-        <v>星辰祝福</v>
+        <v>文昌灵光·开运</v>
       </c>
       <c r="D25" t="str">
         <v>support</v>
@@ -1259,7 +1259,7 @@
         <v>60</v>
       </c>
       <c r="G25" t="str">
-        <v>星辰庇佑，全面提升</v>
+        <v>书画之灵的共鸣让你更易触发连灵</v>
       </c>
       <c r="H25" t="str">
         <v>✨</v>
@@ -1267,7 +1267,7 @@
       <c r="I25" t="str">
         <v>buff</v>
       </c>
-      <c r="O25">
+      <c r="P25">
         <v>20</v>
       </c>
       <c r="S25">
@@ -1285,7 +1285,7 @@
         <v>skill_time_warp</v>
       </c>
       <c r="C26" t="str">
-        <v>时空扭曲</v>
+        <v>时序灵光·折叠</v>
       </c>
       <c r="D26" t="str">
         <v>support</v>
@@ -1297,7 +1297,7 @@
         <v>70</v>
       </c>
       <c r="G26" t="str">
-        <v>扭曲时空，获得时间和速度</v>
+        <v>时序灵光在灵场中折叠，同时延长时间与加速</v>
       </c>
       <c r="H26" t="str">
         <v>🌀</v>
@@ -1305,10 +1305,10 @@
       <c r="I26" t="str">
         <v>time</v>
       </c>
-      <c r="N26">
+      <c r="O26">
         <v>1.5</v>
       </c>
-      <c r="Q26">
+      <c r="R26">
         <v>15</v>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
         <v>skill_divine_shield</v>
       </c>
       <c r="C27" t="str">
-        <v>神圣护盾</v>
+        <v>玉蝉灵光·羽化</v>
       </c>
       <c r="D27" t="str">
         <v>support</v>
@@ -1332,10 +1332,10 @@
         <v>80</v>
       </c>
       <c r="G27" t="str">
-        <v>神圣护盾，免疫伤害5秒</v>
+        <v>玉蝉仙的古灵共鸣——以玉蝉的灵能完全隔绝外界冲击威力</v>
       </c>
       <c r="H27" t="str">
-        <v>😇</v>
+        <v>🛡️</v>
       </c>
       <c r="I27" t="str">
         <v>shield</v>
@@ -1343,7 +1343,7 @@
       <c r="M27">
         <v>100</v>
       </c>
-      <c r="U27">
+      <c r="N27">
         <v>5</v>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
         <v>skill_revival</v>
       </c>
       <c r="C28" t="str">
-        <v>复活</v>
+        <v>灵核归位</v>
       </c>
       <c r="D28" t="str">
         <v>support</v>
@@ -1367,7 +1367,7 @@
         <v>120</v>
       </c>
       <c r="G28" t="str">
-        <v>死亡时自动复活，恢复50%生命</v>
+        <v>被紊乱能量压垮后，古灵强行将你的灵核推回原位</v>
       </c>
       <c r="H28" t="str">
         <v>💫</v>
@@ -1375,10 +1375,10 @@
       <c r="I28" t="str">
         <v>revive</v>
       </c>
-      <c r="V28" t="b">
+      <c r="W28" t="b">
         <v>1</v>
       </c>
-      <c r="W28">
+      <c r="X28">
         <v>50</v>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
         <v>skill_galaxy_blessing</v>
       </c>
       <c r="C29" t="str">
-        <v>星河祝福</v>
+        <v>万灵共鸣</v>
       </c>
       <c r="D29" t="str">
         <v>support</v>
@@ -1402,7 +1402,7 @@
         <v>90</v>
       </c>
       <c r="G29" t="str">
-        <v>星河之力加持，大幅提升属性</v>
+        <v>八座灵域的灵脉短暂共振，所有古灵同时增幅你</v>
       </c>
       <c r="H29" t="str">
         <v>🌟</v>
@@ -1410,7 +1410,7 @@
       <c r="I29" t="str">
         <v>buff</v>
       </c>
-      <c r="O29">
+      <c r="P29">
         <v>30</v>
       </c>
       <c r="S29">
@@ -1419,7 +1419,7 @@
       <c r="T29">
         <v>20</v>
       </c>
-      <c r="X29">
+      <c r="U29">
         <v>0.3</v>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
         <v>skill_void_hide</v>
       </c>
       <c r="C30" t="str">
-        <v>虚空隐匿</v>
+        <v>灵隙潜行</v>
       </c>
       <c r="D30" t="str">
         <v>support</v>
@@ -1443,7 +1443,7 @@
         <v>60</v>
       </c>
       <c r="G30" t="str">
-        <v>消失在虚空中，隐身3秒免疫伤害</v>
+        <v>钻进灵域中两条灵脉之间的微小裂隙——邪灵暂时发现不了你</v>
       </c>
       <c r="H30" t="str">
         <v>🌀</v>
@@ -1451,7 +1451,7 @@
       <c r="I30" t="str">
         <v>immunity</v>
       </c>
-      <c r="U30">
+      <c r="N30">
         <v>3</v>
       </c>
     </row>
@@ -1463,7 +1463,7 @@
         <v>skill_ultimate_invincibility</v>
       </c>
       <c r="C31" t="str">
-        <v>绝对无敌</v>
+        <v>灵域屏障</v>
       </c>
       <c r="D31" t="str">
         <v>support</v>
@@ -1475,7 +1475,7 @@
         <v>150</v>
       </c>
       <c r="G31" t="str">
-        <v>10秒内免疫一切伤害</v>
+        <v>在周身制造一层微型灵域屏障——与外界暂时隔绝能量交换</v>
       </c>
       <c r="H31" t="str">
         <v>👑</v>
@@ -1483,7 +1483,7 @@
       <c r="I31" t="str">
         <v>shield</v>
       </c>
-      <c r="U31">
+      <c r="N31">
         <v>10</v>
       </c>
     </row>
@@ -1495,7 +1495,7 @@
         <v>skill_attack_boost</v>
       </c>
       <c r="C32" t="str">
-        <v>攻击强化</v>
+        <v>灵光亲和</v>
       </c>
       <c r="D32" t="str">
         <v>passive</v>
@@ -1504,7 +1504,7 @@
         <v>R</v>
       </c>
       <c r="G32" t="str">
-        <v>永久增加攻击力</v>
+        <v>与古灵的意义连接加深，灵光冲击威力永久提升</v>
       </c>
       <c r="H32" t="str">
         <v>⚔️</v>
@@ -1524,7 +1524,7 @@
         <v>skill_crit_sense</v>
       </c>
       <c r="C33" t="str">
-        <v>暴击感知</v>
+        <v>会心感应</v>
       </c>
       <c r="D33" t="str">
         <v>passive</v>
@@ -1533,7 +1533,7 @@
         <v>R</v>
       </c>
       <c r="G33" t="str">
-        <v>永久增加暴击率</v>
+        <v>对邪灵紊乱核心的感知力增强</v>
       </c>
       <c r="H33" t="str">
         <v>👁️</v>
@@ -1553,7 +1553,7 @@
         <v>skill_gold_finder</v>
       </c>
       <c r="C34" t="str">
-        <v>寻宝者</v>
+        <v>灵质引力</v>
       </c>
       <c r="D34" t="str">
         <v>passive</v>
@@ -1562,7 +1562,7 @@
         <v>R</v>
       </c>
       <c r="G34" t="str">
-        <v>金币掉落增加50%</v>
+        <v>灵场对灵质碎片的吸附力增强</v>
       </c>
       <c r="H34" t="str">
         <v>💰</v>
@@ -1570,7 +1570,7 @@
       <c r="I34" t="str">
         <v>passive</v>
       </c>
-      <c r="P34">
+      <c r="Q34">
         <v>1.5</v>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
         <v>skill_exp_boost</v>
       </c>
       <c r="C35" t="str">
-        <v>经验加成</v>
+        <v>灵脉领悟</v>
       </c>
       <c r="D35" t="str">
         <v>passive</v>
@@ -1591,7 +1591,7 @@
         <v>R</v>
       </c>
       <c r="G35" t="str">
-        <v>经验获取增加30%</v>
+        <v>在灵域中的深入探索让你对灵脉的理解加速</v>
       </c>
       <c r="H35" t="str">
         <v>📚</v>
@@ -1611,7 +1611,7 @@
         <v>skill_crit_master</v>
       </c>
       <c r="C36" t="str">
-        <v>暴击精通</v>
+        <v>会心贯通</v>
       </c>
       <c r="D36" t="str">
         <v>passive</v>
@@ -1620,10 +1620,10 @@
         <v>SR</v>
       </c>
       <c r="G36" t="str">
-        <v>永久增加暴击率</v>
+        <v>对邪灵紊乱核心的精确直觉大幅提升</v>
       </c>
       <c r="H36" t="str">
-        <v>🎯</v>
+        <v>🔮</v>
       </c>
       <c r="I36" t="str">
         <v>passive</v>
@@ -1640,7 +1640,7 @@
         <v>skill_crit_damage_master</v>
       </c>
       <c r="C37" t="str">
-        <v>爆伤精通</v>
+        <v>暴击会心</v>
       </c>
       <c r="D37" t="str">
         <v>passive</v>
@@ -1649,15 +1649,15 @@
         <v>SR</v>
       </c>
       <c r="G37" t="str">
-        <v>永久增加暴击伤害</v>
+        <v>直击紊乱核心造成的破坏更大</v>
       </c>
       <c r="H37" t="str">
-        <v>💎</v>
+        <v>🪨</v>
       </c>
       <c r="I37" t="str">
         <v>passive</v>
       </c>
-      <c r="X37">
+      <c r="U37">
         <v>0.25</v>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
         <v>skill_attack_master</v>
       </c>
       <c r="C38" t="str">
-        <v>攻击大师</v>
+        <v>灵光驾驭</v>
       </c>
       <c r="D38" t="str">
         <v>passive</v>
@@ -1678,7 +1678,7 @@
         <v>SR</v>
       </c>
       <c r="G38" t="str">
-        <v>永久大幅增加攻击力</v>
+        <v>灵光的掌控力大幅提升</v>
       </c>
       <c r="H38" t="str">
         <v>🗡️</v>
@@ -1698,7 +1698,7 @@
         <v>skill_defense_master</v>
       </c>
       <c r="C39" t="str">
-        <v>防御大师</v>
+        <v>灵域护体</v>
       </c>
       <c r="D39" t="str">
         <v>passive</v>
@@ -1707,7 +1707,7 @@
         <v>SR</v>
       </c>
       <c r="G39" t="str">
-        <v>永久增加防御和生命</v>
+        <v>更善于将残余灵能转化为身体防御</v>
       </c>
       <c r="H39" t="str">
         <v>🛡️</v>
@@ -1715,7 +1715,7 @@
       <c r="I39" t="str">
         <v>passive</v>
       </c>
-      <c r="R39">
+      <c r="V39">
         <v>30</v>
       </c>
       <c r="Z39">
@@ -1730,7 +1730,7 @@
         <v>skill_star_affinity</v>
       </c>
       <c r="C40" t="str">
-        <v>星辰亲和</v>
+        <v>灵场亲和</v>
       </c>
       <c r="D40" t="str">
         <v>passive</v>
@@ -1739,7 +1739,7 @@
         <v>SR</v>
       </c>
       <c r="G40" t="str">
-        <v>星星分数增加50%</v>
+        <v>灵场更自然地吸引周围灵光</v>
       </c>
       <c r="H40" t="str">
         <v>⭐</v>
@@ -1747,7 +1747,7 @@
       <c r="I40" t="str">
         <v>passive</v>
       </c>
-      <c r="AA40">
+      <c r="AC40">
         <v>1.5</v>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
         <v>skill_combo_master</v>
       </c>
       <c r="C41" t="str">
-        <v>连击大师</v>
+        <v>连灵精通</v>
       </c>
       <c r="D41" t="str">
         <v>passive</v>
@@ -1768,7 +1768,7 @@
         <v>SSR</v>
       </c>
       <c r="G41" t="str">
-        <v>连击伤害加成提升50%</v>
+        <v>连灵灵光更容易触发</v>
       </c>
       <c r="H41" t="str">
         <v>🔗</v>
@@ -1776,7 +1776,7 @@
       <c r="I41" t="str">
         <v>passive</v>
       </c>
-      <c r="AB41">
+      <c r="AA41">
         <v>0.5</v>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
         <v>skill_berserker</v>
       </c>
       <c r="C42" t="str">
-        <v>狂战士</v>
+        <v>鼎纹战意</v>
       </c>
       <c r="D42" t="str">
         <v>passive</v>
@@ -1797,7 +1797,7 @@
         <v>SSR</v>
       </c>
       <c r="G42" t="str">
-        <v>狂暴之力，大幅提升攻击属性</v>
+        <v>龙纹鼎灵的古灵共鸣——战斗中更忘我</v>
       </c>
       <c r="H42" t="str">
         <v>😤</v>
@@ -1811,7 +1811,7 @@
       <c r="T42">
         <v>15</v>
       </c>
-      <c r="X42">
+      <c r="U42">
         <v>0.3</v>
       </c>
     </row>
@@ -1823,7 +1823,7 @@
         <v>skill_iron_will</v>
       </c>
       <c r="C43" t="str">
-        <v>钢铁意志</v>
+        <v>剑魄意志</v>
       </c>
       <c r="D43" t="str">
         <v>passive</v>
@@ -1832,7 +1832,7 @@
         <v>SSR</v>
       </c>
       <c r="G43" t="str">
-        <v>钢铁般的意志，全面提升防御</v>
+        <v>剑魄的古灵共鸣——紊乱能量更难撼动你</v>
       </c>
       <c r="H43" t="str">
         <v>🧱</v>
@@ -1843,7 +1843,7 @@
       <c r="M43">
         <v>20</v>
       </c>
-      <c r="R43">
+      <c r="V43">
         <v>50</v>
       </c>
       <c r="Z43">
@@ -1858,7 +1858,7 @@
         <v>skill_fortune_master</v>
       </c>
       <c r="C44" t="str">
-        <v>财富大师</v>
+        <v>金乌赐福</v>
       </c>
       <c r="D44" t="str">
         <v>passive</v>
@@ -1867,7 +1867,7 @@
         <v>SSR</v>
       </c>
       <c r="G44" t="str">
-        <v>金币翻倍，掉落率提升</v>
+        <v>金乌灵盘旋期间，掉落灵币显著增加</v>
       </c>
       <c r="H44" t="str">
         <v>🤑</v>
@@ -1875,10 +1875,10 @@
       <c r="I44" t="str">
         <v>passive</v>
       </c>
-      <c r="P44">
+      <c r="Q44">
         <v>2</v>
       </c>
-      <c r="AC44">
+      <c r="AB44">
         <v>1.5</v>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
         <v>skill_shadow_evasion</v>
       </c>
       <c r="C45" t="str">
-        <v>暗影闪避</v>
+        <v>玉蝉蜕壳</v>
       </c>
       <c r="D45" t="str">
         <v>passive</v>
@@ -1899,7 +1899,7 @@
         <v>SSR</v>
       </c>
       <c r="G45" t="str">
-        <v>受到攻击时20%概率完全闪避</v>
+        <v>玉蝉仙的古灵共鸣——紊乱能量有时会从你身边滑过</v>
       </c>
       <c r="H45" t="str">
         <v>👤</v>
@@ -1919,7 +1919,7 @@
         <v>skill_galaxy_power</v>
       </c>
       <c r="C46" t="str">
-        <v>星河之力</v>
+        <v>全灵共鸣</v>
       </c>
       <c r="D46" t="str">
         <v>passive</v>
@@ -1928,10 +1928,10 @@
         <v>UR</v>
       </c>
       <c r="G46" t="str">
-        <v>星河之力加持，终极属性提升</v>
+        <v>所有已连接古灵的灵脉共振达到最高</v>
       </c>
       <c r="H46" t="str">
-        <v>🌌</v>
+        <v>🔮</v>
       </c>
       <c r="I46" t="str">
         <v>passive</v>
@@ -1942,7 +1942,7 @@
       <c r="T46">
         <v>25</v>
       </c>
-      <c r="X46">
+      <c r="U46">
         <v>0.5</v>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
         <v>skill_omnipotent</v>
       </c>
       <c r="C47" t="str">
-        <v>全能</v>
+        <v>唤灵贯通</v>
       </c>
       <c r="D47" t="str">
         <v>passive</v>
@@ -1963,7 +1963,7 @@
         <v>UR</v>
       </c>
       <c r="G47" t="str">
-        <v>全能之神，所有属性全面提升</v>
+        <v>跨越八座灵域的唤灵人——所有古灵的力量在你身上交汇</v>
       </c>
       <c r="H47" t="str">
         <v>🌟</v>
@@ -1971,11 +1971,8 @@
       <c r="I47" t="str">
         <v>passive</v>
       </c>
-      <c r="P47">
+      <c r="Q47">
         <v>2</v>
-      </c>
-      <c r="R47">
-        <v>50</v>
       </c>
       <c r="S47">
         <v>50</v>
@@ -1983,8 +1980,11 @@
       <c r="T47">
         <v>20</v>
       </c>
-      <c r="X47">
+      <c r="U47">
         <v>0.4</v>
+      </c>
+      <c r="V47">
+        <v>50</v>
       </c>
       <c r="Z47">
         <v>100</v>
@@ -1998,7 +1998,7 @@
         <v>skill_void_power</v>
       </c>
       <c r="C48" t="str">
-        <v>虚空之力</v>
+        <v>灵脉之力</v>
       </c>
       <c r="D48" t="str">
         <v>passive</v>
@@ -2007,7 +2007,7 @@
         <v>UR</v>
       </c>
       <c r="G48" t="str">
-        <v>虚空之力加持，大幅提升输出能力</v>
+        <v>对灵脉本身的理解加深——灵脉的碎片为你所用</v>
       </c>
       <c r="H48" t="str">
         <v>🌀</v>
@@ -2021,7 +2021,7 @@
       <c r="T48">
         <v>15</v>
       </c>
-      <c r="X48">
+      <c r="U48">
         <v>0.4</v>
       </c>
     </row>
@@ -2033,7 +2033,7 @@
         <v>skill_star_spark</v>
       </c>
       <c r="C49" t="str">
-        <v>星火</v>
+        <v>微灵光</v>
       </c>
       <c r="D49" t="str">
         <v>attack</v>
@@ -2045,7 +2045,7 @@
         <v>20</v>
       </c>
       <c r="G49" t="str">
-        <v>发射微弱星火，造成少量伤害</v>
+        <v>最基础的灵光投射，古灵以最微弱的共鸣协助</v>
       </c>
       <c r="H49" t="str">
         <v>✨</v>
@@ -2065,7 +2065,7 @@
         <v>skill_minor_heal</v>
       </c>
       <c r="C50" t="str">
-        <v>微光治愈</v>
+        <v>微愈灵光</v>
       </c>
       <c r="D50" t="str">
         <v>support</v>
@@ -2077,7 +2077,7 @@
         <v>30</v>
       </c>
       <c r="G50" t="str">
-        <v>微弱星光治愈，恢复少量生命</v>
+        <v>最基础的灵光修复</v>
       </c>
       <c r="H50" t="str">
         <v>💚</v>
@@ -2097,7 +2097,7 @@
         <v>skill_star_sense</v>
       </c>
       <c r="C51" t="str">
-        <v>星感</v>
+        <v>灵感</v>
       </c>
       <c r="D51" t="str">
         <v>passive</v>
@@ -2106,7 +2106,7 @@
         <v>UC</v>
       </c>
       <c r="G51" t="str">
-        <v>永久增加少量攻击力</v>
+        <v>对灵光的直觉提高了</v>
       </c>
       <c r="H51" t="str">
         <v>🌟</v>
@@ -2126,7 +2126,7 @@
         <v>skill_big_bang</v>
       </c>
       <c r="C52" t="str">
-        <v>宇宙大爆炸</v>
+        <v>源灵回响</v>
       </c>
       <c r="D52" t="str">
         <v>attack</v>
@@ -2138,7 +2138,7 @@
         <v>120</v>
       </c>
       <c r="G52" t="str">
-        <v>引爆星球造成毁灭伤害，眩慕3秒</v>
+        <v>模拟大地之源灵域的第一次意义投射——不是毁灭的爆炸，是意义被赋予时的回响</v>
       </c>
       <c r="H52" t="str">
         <v>💥</v>
@@ -2158,7 +2158,7 @@
         <v>skill_singularity</v>
       </c>
       <c r="C53" t="str">
-        <v>奇点</v>
+        <v>灵脉奇点</v>
       </c>
       <c r="D53" t="str">
         <v>support</v>
@@ -2170,7 +2170,7 @@
         <v>180</v>
       </c>
       <c r="G53" t="str">
-        <v>黑洞奇点，5秒吸收伤害转护盾后反弹50%</v>
+        <v>灵脉中特定的共振节点——吸收冲击威力、储存能量、然后反弹</v>
       </c>
       <c r="H53" t="str">
         <v>🌀</v>
@@ -2178,7 +2178,7 @@
       <c r="I53" t="str">
         <v>shield</v>
       </c>
-      <c r="O53">
+      <c r="P53">
         <v>5</v>
       </c>
     </row>
@@ -2190,7 +2190,7 @@
         <v>skill_transcendence</v>
       </c>
       <c r="C54" t="str">
-        <v>超越</v>
+        <v>灵域行者</v>
       </c>
       <c r="D54" t="str">
         <v>passive</v>
@@ -2199,7 +2199,7 @@
         <v>LR</v>
       </c>
       <c r="G54" t="str">
-        <v>全属性大幅提升，每击杀10怪永久+1攻击（上限50）</v>
+        <v>跨越多座灵域的历练使灵场自然强化——每一条新灵脉都是新的能量来源</v>
       </c>
       <c r="H54" t="str">
         <v>🔱</v>
@@ -2207,17 +2207,17 @@
       <c r="I54" t="str">
         <v>passive</v>
       </c>
-      <c r="R54">
-        <v>60</v>
-      </c>
       <c r="S54">
         <v>120</v>
       </c>
       <c r="T54">
         <v>30</v>
       </c>
-      <c r="X54">
+      <c r="U54">
         <v>0.6</v>
+      </c>
+      <c r="V54">
+        <v>60</v>
       </c>
       <c r="Z54">
         <v>120</v>
@@ -2231,7 +2231,7 @@
         <v>skill_stardust_parade</v>
       </c>
       <c r="C55" t="str">
-        <v>星尘巡游</v>
+        <v>星尘灵光·巡游</v>
       </c>
       <c r="D55" t="str">
         <v>attack</v>
@@ -2243,7 +2243,7 @@
         <v>90</v>
       </c>
       <c r="G55" t="str">
-        <v>流星雨5秒持续伤害，点击星星额外触发伤害</v>
+        <v>一连串微小灵光持续追打邪灵，压制紊乱波动</v>
       </c>
       <c r="H55" t="str">
         <v>🎇</v>
@@ -2254,7 +2254,7 @@
       <c r="J55">
         <v>200</v>
       </c>
-      <c r="O55">
+      <c r="P55">
         <v>5</v>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
         <v>skill_lucky_constellation</v>
       </c>
       <c r="C56" t="str">
-        <v>幸运星座</v>
+        <v>文曲灵光·星阵</v>
       </c>
       <c r="D56" t="str">
         <v>support</v>
@@ -2278,15 +2278,15 @@
         <v>100</v>
       </c>
       <c r="G56" t="str">
-        <v>随机星座祝福（攻击+30%/全回复/时间+10s/金币x3）</v>
+        <v>古灵在灵场上划出的短暂祝福区域</v>
       </c>
       <c r="H56" t="str">
-        <v>🎰</v>
+        <v>🔮</v>
       </c>
       <c r="I56" t="str">
         <v>buff</v>
       </c>
-      <c r="O56">
+      <c r="P56">
         <v>15</v>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
         <v>skill_seasons_blessing</v>
       </c>
       <c r="C57" t="str">
-        <v>赛季星辰</v>
+        <v>赛季灵场</v>
       </c>
       <c r="D57" t="str">
         <v>passive</v>
@@ -2307,7 +2307,7 @@
         <v>SP</v>
       </c>
       <c r="G57" t="str">
-        <v>赛季期间星星分数+15%，连击分数+10%</v>
+        <v>在本赛季的灵域主题下，灵场与灵域更加契合</v>
       </c>
       <c r="H57" t="str">
         <v>🎪</v>
@@ -2316,10 +2316,10 @@
         <v>passive</v>
       </c>
       <c r="AA57">
+        <v>0.1</v>
+      </c>
+      <c r="AC57">
         <v>1.15</v>
-      </c>
-      <c r="AB57">
-        <v>0.1</v>
       </c>
     </row>
   </sheetData>
